--- a/wp-plugin/rtap/data/questions-for-review.xlsx
+++ b/wp-plugin/rtap/data/questions-for-review.xlsx
@@ -3688,7 +3688,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>'Gauge pressure' — избыточное давление (давление сверх атмосферного); 'absolute pressure' — абсолютное.</t>
+          <t>"Gauge pressure" = "избыточное давление" (разность между абсолютным давлением и атмосферным). Оба варианта — "избыточное давление" и "манометрическое давление" — встречаются в нормативных документах, однако "избыточное давление" является более широко используемым термином в ГОСТ Р 8.000.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Вариант 3 точен: 'cross pattern' — крест-накрест; 'specified torque value' — нормируемый момент затяжки (нормативный термин).</t>
+          <t>"Fasteners" — крепёжные элементы (родовой термин: болты, винты, шпильки). Перевод "болты" ошибочно сужает понятие. "Указанного значения крутящего момента" точнее "нормируемого" для инструкции по эксплуатации.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Вариант 3: 'structural members' — несущие элементы; 'equivalent' — равнозначный (точнее 'эквивалентный' в нормативном контексте).</t>
+          <t>"Structural members" — конструктивные элементы (не "несущие": не все конструктивные элементы являются несущими). "Эквивалентному" точнее "равнозначному" в нормативном контексте.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>'Passivation' — пассивация (образование защитной оксидной плёнки; ГОСТ 9.305 — пассивирование как процесс).</t>
+          <t>По ГОСТ 9.305-84 нормативный термин для данного процесса — "пассивирование". "Пассивация" встречается в разговорной профессиональной речи, но не является нормативным термином стандарта.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>'Work hardening' — наклёп (упрочнение металла при пластической деформации без нагрева; ГОСТ 18394).</t>
+          <t>"Work hardening" = "наклёп" (поверхностное упрочнение при холодной обработке). Также принят термин "деформационное упрочнение" — более широкое понятие, применяется в контексте международных стандартов. В зависимости от контекста оба варианта допустимы; "наклёп" предпочтительнее для описания поверхностной обработки.</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>'Running state' — рабочее состояние / состояние «работа»; перевод 'состояния работы' неестественен для технической документации АСУТП. Правильно: 'состояние «Работа»' или 'рабочее состояние конвейера'.</t>
+          <t>"Рабочем режиме" — добавление, отсутствующее в источнике ("to maintain the conveyor running state"). Переводчик добавил избыточный элемент "в рабочем режиме", дублирующий смысл уже переведённого "состояния работы". Добавление текста без основания в источнике — грубая переводческая ошибка.</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>[1, 3, 2, 0]</t>
+          <t>[0, 1, 3, 2]</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: субъект → предикат → уточнение периодичности → цель. 'Система... должна подвергаться... ежегодному... для обеспечения...'</t>
+          <t>Правильный порядок: начало предложения с подлежащим → сказуемое с обстоятельством времени → указание цели (для обеспечения) → результат (эффективности против коррозии).</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>[2, 0, 3, 1]</t>
+          <t>[2, 0, 1]</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: действие → место → ожидание → результат. Однако варианты 3 и 4 конкурируют — правильный: 'отделена... → помещена → в ожидании → до принятия решения'.</t>
+          <t>Несоответствующая продукция должна быть: 1) отделена и промаркирована, 2) помещена в карантинную зону, 3) удерживаться там до принятия решения о дальнейшей судьбе. Термин "disposition" = "решение о судьбе/утилизации продукции".</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>[2, 1, 3, 0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: условие → действие → уточнение → цель. 'До первого пуска система смазки должна быть промыта... для удаления...'</t>
+          <t>Правильный порядок передаёт структуру оригинала: обстоятельство времени ("до первого пуска") + сказуемое ("должна быть промыта") + цель ("для удаления...") + место ("из масляных каналов").</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>'Dielectric strength' — электрическая прочность (правильно), НО в контексте изоляции точнее: 'электрическая прочность изоляции' или 'пробивное напряжение'. Однако ключевая ошибка: 'dielectric strength' иногда смешивают с 'insulation resistance'. Здесь 'электрической прочности' — допустимо, но 'диэлектрической прочности' — предпочтительнее для изоляционных материалов.</t>
+          <t>Стандартное русское название процесса VPI (vacuum pressure impregnation) — "пропитка под вакуумом и давлением" или "вакуумно-нагнетательная пропитка". Порядок "давлением под вакуумом" переставляет акценты. "Электрическая прочность" — принятый перевод "dielectric strength" по ГОСТ IEC 60243-1.</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>'Proof of concept' — подтверждение концепции (или «демонстрация осуществимости»); в НИОКР — доказательство концепции.</t>
+          <t>"Proof of concept" (PoC) в контексте НИОКР переводится как "доказательство концепции". Вариант "подтверждение осуществимости" ближе к "proof of feasibility". "Подтверждение концепции" — тоже допустимо, но "доказательство концепции" закрепилось как стандарт в технической литературе.</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Соглашение толкуется в соответствии с законодательством Англии и Уэльса, за исключением его коллизионных норм.</t>
+          <t>Соглашение толкуется в соответствии с правом Англии и Уэльса, за исключением его коллизионных норм.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>'Jointly and severally liable' — солидарная и субсидиарная ответственность (или просто «солидарно»). В русском праве «солидарная ответственность» означает, что каждый должник несёт ответственность в полном объёме. Перевод должен звучать «несёт солидарную ответственность», однако пропущен элемент 'severally' — раздельная ответственность. Точный перевод: «несёт солидарную ответственность» (что охватывает оба аспекта в российском праве).</t>
+          <t>«Jointly and severally liable» = «несёт солидарную ответственность» (ГК РФ ст. 322–325: каждый должник отвечает за обязательство в целом). Добавление «субсидиарную» — грубая ошибка: субсидиарная ответственность (ст. 399 ГК РФ) наступает лишь при невозможности исполнения основным должником и не является частью «jointly and severally».</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -16746,12 +16746,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 0]</t>
+          <t>[1, 2, 0]</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: (1) вводная конструкция 'В случае если…', (2) 'будет признано…', (3) повтор начала следствия, (0) окончание. Логика: придаточное условия → главная часть со следствием.</t>
+          <t>Правильный порядок: «В случае если какое-либо положение настоящего Соглашения → признано недействительным или неисполнимым судом → такое положение подлежит изменению в минимально необходимой степени для обеспечения его действительности и исполнимости.» Сегмент [3] — усечённый вариант-дистрактор сегмента [0].</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок по смыслу Венской конвенции о праве международных договоров (ст. 27): (1) субъект + запрет, затем (3) или (0) — уточнение. Сегмент (2) отсутствует в данной норме.</t>
+          <t>Правильный порядок: «Государство не вправе → ссылаться на положения своего внутреннего законодательства → в качестве оправдания неисполнения обязательств по международному договору.» (ст. 27 Венской конвенции о праве международных договоров). Сегмент [0] («как основание для невыполнения договора») — устаревший/неполный дубль сегмента [3], его включение создало бы повтор. Сегмент [2] отражает смысл, отсутствующий в источнике.</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Ответная сторона опровергает все утверждения и предъявляет встречные требования о взыскании убытков на сумму 2 000 000 долларов США.</t>
+          <t>Ответчик опровергает все утверждения и предъявляет встречные требования о взыскании убытков на сумму 2 000 000 долларов США.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Вариант 2 точен: «опровергает» точнее для 'denies'; «предъявляет встречные требования» — юридически точная формулировка; сумма прописана формально. Вариант 1 — «обвинения» (accusations) вместо «утверждений» (allegations). Вариант 3 — «контртребование» — устаревшее слово.</t>
+          <t>«Respondent» в международном арбитраже и судопроизводстве = «ответчик» (используется в ICC, LCIA, МКАС, ППТРФ). «Ответная сторона» не является устоявшимся юридическим термином. «Allegations» = «утверждения» (в правовом контексте), не «обвинения» (которые относятся к уголовному праву).</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -20108,12 +20108,12 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>'Force of law' — юридическая сила: свойство нормативного или судебного акта быть обязательным и влечь правовые последствия.</t>
+          <t>Применительно к судебному решению используется термин «законная сила» (ГПК РФ ст. 209, АПК РФ ст. 180): «решение вступает в законную силу». «Юридическая сила» — общий термин для любых правовых актов (законов, договоров). В процессуальном контексте корректен только термин «законная сила».</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -24855,12 +24855,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Вариант 1: «нейтропения 3 степени» — стандартная форма для grade 3 по шкале NCI-CTCAE. «Цикл» точнее «курса» в контексте химиотерапии. Вариант 2 упускает числовую степень. Вариант 3 грамматически верен, но «степени тяжести» избыточно.</t>
+          <t>По стандарту NCI-CTCAE и клинической практике "cycle" = "цикл" (не "курс"). "Курс" в русской онкологии обозначает всю программу лечения, тогда как "цикл" — один повторяющийся временной блок. "Нейтропения третьей степени тяжести" — принятая формулировка по шкале токсичности CTCAE.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Все три сегмента правильны. Однако в контексте — ошибки нет, все варианты корректны. (Тестовая ловушка: вариант «эмпирическая» верен — empirical therapy означает лечение, начатое до получения результатов культуры.) Данный вопрос проверяет умение распознать отсутствие ошибки и знание термина 'empirical antibiotic therapy'.</t>
+          <t>"Empirical" в медицинском контексте = "эмпирическая" (терапия, назначенная до получения результатов посева на основе клинической картины). "Профилактическая" означает preventive и кардинально меняет смысл: антибиотик назначен не для профилактики, а как ответ на инфекцию с неизвестным возбудителем.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -26576,7 +26576,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «перед началом химиотерапии» → «Обязательна тщательная оценка функции почек и печени» → «необходимо провести тщательную оценку функции почек и печени» → «для обоснования коррекции доз.» Примечание: данный пример демонстрирует структурное построение фразы.</t>
+          <t>Правильный порядок: обстоятельство времени → подлежащее/сказуемое → цель (минимизации риска) → уточнение (коррекция доз).</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -26687,12 +26687,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 0]</t>
+          <t>[1, 2, 0]</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «У пациентов с прогрессированием заболевания» → «на фоне терапии первой линии» → «необходимо провести оценку и» → «следует рассмотреть варианты терапии второй линии.»</t>
+          <t>У пациентов с прогрессированием на терапии первой линии следует рассмотреть варианты терапии второй линии. Единый модальный предикат "следует рассмотреть" соответствует "should be evaluated for" из источника.</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -26803,12 +26803,12 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>[2, 1, 0, 3]</t>
+          <t>[2, 1, 0]</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Была выполнена биопсия ткани» → «для подтверждения диагноза» → «диффузной крупноклеточной B-клеточной лимфомы.» Сегмент 3 избыточен и не входит в корректный перевод.</t>
+          <t>Правильный порядок: "Была выполнена биопсия ткани → для подтверждения диагноза → диффузной крупноклеточной B-клеточной лимфомы." Сегмент [3] — лишний дистрактор.</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -27383,12 +27383,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>[2, 1, 0, 3]</t>
+          <t>[2, 1, 3, 0]</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Протокол требует документирования» → «всех серьёзных нежелательных явлений» → «в течение 24 часов с момента осведомления исследователя.» Сегмент 3 уточняет, но логически следует в конце.</t>
+          <t>Правильный порядок: "Протокол требует → документирования всех СНЯ → в течение 24 часов с момента осведомления исследователя → о факте их возникновения." Так сегмент [3] органично завершает предложение.</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -27673,12 +27673,12 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>[1, 3, 0, 2]</t>
+          <t>[1, 3, 0]</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Максимально переносимая доза» → «была определена» → «в ходе исследования I фазы с эскалацией дозы.» Сегмент 2 — синоним, не входящий в основной перевод.</t>
+          <t>Правильный порядок: "Максимально переносимая доза → была определена → в ходе исследования I фазы с эскалацией дозы." Сегмент [2] — дистрактор (синонимичная формулировка).</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -27847,12 +27847,12 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>[2, 1, 0, 3]</t>
+          <t>[2, 1, 0]</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Выживаемость без прогрессирования» → «была значимо продолжительнее в группе лечения» → «по сравнению с группой плацебо.» Сегмент 3 — альтернативный вариант, не входящий в основной перевод.</t>
+          <t>Правильный порядок: "Выживаемость без прогрессирования → была значимо продолжительнее → в группе лечения по сравнению с группой плацебо." Сегмент [3] — дистрактор.</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -28079,12 +28079,12 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>[1, 2, 0, 3]</t>
+          <t>[1, 2, 0]</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Применение препарата вне зарегистрированных показаний» → «при тревожных расстройствах» → «было задокументировано в медицинской карте пациента.» Сегмент 3 — описательный вариант, не входящий в основной перевод.</t>
+          <t>Правильный порядок: "Применение препарата вне зарегистрированных показаний → при тревожных расстройствах → было задокументировано в медицинской карте пациента." Сегмент [3] — дистрактор.</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -28195,12 +28195,12 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>[2, 1, 0, 3]</t>
+          <t>[2, 1, 3, 0]</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Согласно руководящим принципам Надлежащей клинической практики,» → «первичная документация должна храниться» → «на срок не менее 15 лет.» Сегмент 3 уточняет место хранения.</t>
+          <t>Правильный порядок: "Согласно принципам НКП → первичная документация должна храниться → в архиве учреждения → на срок не менее 15 лет." Сегмент [3] уточняет место хранения и стоит перед сроком.</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -29875,12 +29875,12 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>[1, 2, 0, 3]</t>
+          <t>[1, 2, 0]</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>Правильный порядок: «Индукция ферментов цитохрома P450» → «рифампицином» → «значимо снижает плазменные концентрации совместно вводимых препаратов.» Сегмент 3 — синоним сегмента 1.</t>
+          <t>Правильный порядок: "Индукция ферментов CYP450 рифампицином → значимо снижает → плазменные концентрации совместно вводимых препаратов." Сегмент [3] — синоним-дистрактор.</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -33201,7 +33201,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>«Access denied» в системных сообщениях Microsoft переводится как «Отказано в доступе» или «Доступ запрещён». Первый вариант принят в Windows.</t>
+          <t>"Access denied" в Windows локализуется как "Доступ запрещён". Вариант "Отказано в доступе" встречается в отдельных системах, но "Доступ запрещён" — наиболее распространённая стандартная форма в пользовательском интерфейсе.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -36464,7 +36464,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -37010,7 +37010,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>[1, 3, 0]</t>
+          <t>[1, 2, 0]</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -38167,7 +38167,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>«Refactor» как глагол переводится «проведите рефакторинг» или «отрефакторьте» (разг.). «Выполните рефакторинг» — несколько громоздко, но допустимо. Однако точнее — «Проведите рефакторинг устаревшей кодовой базы...»</t>
+          <t>"Рефакторизация" — неверная форма; правильно "рефакторинг". "Выполните рефакторинг устаревшей кодовой базы" — стандартная формулировка в русскоязычной документации.</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -38290,12 +38290,12 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>«Data in transit» — «данные в пути» или «данные при передаче». Однако принятый стандартный термин в документации по ИБ — «данные при передаче» или «передаваемые данные». Реальная ошибка в том, что устоявшийся термин — «данные в движении» или «данные при передаче» в контексте классификации: data at rest / data in transit / data in use.</t>
+          <t>"Man-in-the-middle attacks" переводится как "атаки типа «человек посередине»" или "атаки «посредник»". Вариант "атак посредника" — неполная нестандартная форма. "Данные при передаче" — стандартный термин для "data in transit".</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -40162,12 +40162,12 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>«Unit tests» — модульные тесты. Это правильный и стандартный перевод. Однако «развёртываемый артефакт» для «deployable artifact» — это дословный перевод; правильнее «артефакт развёртывания». Тем не менее реальная проблема — «модульные тесты» иногда переводится как «юнит-тесты» в неформальной среде. Правильный перевод unit tests — «модульные тесты».</t>
+          <t>"Deployable artifact" следует переводить как "артефакт развёртывания" (существительное + генитив), а не "развёртываемый артефакт" (причастие + существительное), как принято в русскоязычной CI/CD документации.</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -40621,7 +40621,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>«User accounts» — учётные записи пользователей. Это правильный перевод. «Контроллеры домена» и «настройте» тоже верны. Однако «учётных записей пользователей» — правильная форма, но в контексте Microsoft предпочтительнее просто «учётных записей» (так как «пользователей» подразумевается в контексте LDAP-каталога).</t>
+          <t>"Аккаунт" — разговорный/заимствованный термин; в профессиональной IT-документации Microsoft принят термин "учётная запись". Вариант "аккаунтов пользователей" недопустим в официальных переводах.</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
